--- a/재정학/03_Exams/[1] midterm/오전반 시험 결과 및 성적/재정학 오전반_final.xlsx
+++ b/재정학/03_Exams/[1] midterm/오전반 시험 결과 및 성적/재정학 오전반_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\03_Exams\[1] midterm\오전반 시험 결과 및 성적\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9743B1EE-1DF6-464F-AD51-DE43D444478C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DEC721-8AEA-474B-BC79-87FD3C2E5E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="중간고사 원본" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'중간고사 통계'!$A$4:$L$4</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'중간고사 통계'!$E$5:$E$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="90">
   <si>
     <t>순번</t>
   </si>
@@ -283,6 +282,82 @@
   </si>
   <si>
     <t>합계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>외국인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>100환산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠진시간</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출석시간</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -290,7 +365,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -332,13 +407,37 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -353,12 +452,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1578,6 +1682,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:T34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1629,21 +1736,17 @@
       <c r="G4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="H4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
       <c r="S4" s="3" t="s">
         <v>78</v>
       </c>
@@ -1655,7 +1758,7 @@
       <c r="A5">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
@@ -1674,17 +1777,16 @@
         <f>E5+F5</f>
         <v>183</v>
       </c>
+      <c r="H5">
+        <f>G5/2</f>
+        <v>91.5</v>
+      </c>
       <c r="I5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+        <f>45-I5</f>
+        <v>37</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>75</v>
@@ -1702,7 +1804,7 @@
       <c r="A6">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C6" t="s">
@@ -1721,17 +1823,16 @@
         <f>E6+F6</f>
         <v>171</v>
       </c>
+      <c r="H6">
+        <f>G6/2</f>
+        <v>85.5</v>
+      </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+        <f>45-I6</f>
+        <v>42</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>76</v>
@@ -1749,7 +1850,7 @@
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
@@ -1768,24 +1869,23 @@
         <f>E7+F7</f>
         <v>163</v>
       </c>
+      <c r="H7">
+        <f>G7/2</f>
+        <v>81.5</v>
+      </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+        <f>45-I7</f>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C8" t="s">
@@ -1804,24 +1904,23 @@
         <f>E8+F8</f>
         <v>145</v>
       </c>
+      <c r="H8">
+        <f>G8/2</f>
+        <v>72.5</v>
+      </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+        <f>45-I8</f>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C9" t="s">
@@ -1840,24 +1939,23 @@
         <f>E9+F9</f>
         <v>140.5</v>
       </c>
+      <c r="H9">
+        <f>G9/2</f>
+        <v>70.25</v>
+      </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+        <f>45-I9</f>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
@@ -1876,60 +1974,83 @@
         <f>E10+F10</f>
         <v>134.5</v>
       </c>
+      <c r="H10">
+        <f>G10/2</f>
+        <v>67.25</v>
+      </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+        <f>45-I10</f>
+        <v>44</v>
+      </c>
+      <c r="Q10">
+        <v>30</v>
+      </c>
+      <c r="R10" s="5">
+        <f>$Q$10*T10</f>
+        <v>9</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="T10">
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="A11" s="9">
         <v>16</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11">
+      <c r="D11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="9">
         <v>59.5</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="9">
         <v>65</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="9">
         <f>E11+F11</f>
         <v>124.5</v>
       </c>
-      <c r="I11">
+      <c r="H11" s="9">
+        <f>G11/2</f>
+        <v>62.25</v>
+      </c>
+      <c r="I11" s="9">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+        <f>45-I11</f>
+        <v>45</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="R11" s="5">
+        <f t="shared" ref="R11:R12" si="0">$Q$10*T11</f>
+        <v>12</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="T11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
@@ -1948,24 +2069,33 @@
         <f>E12+F12</f>
         <v>123.5</v>
       </c>
+      <c r="H12">
+        <f>G12/2</f>
+        <v>61.75</v>
+      </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+        <f>45-I12</f>
+        <v>45</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12">
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C13" t="s">
@@ -1984,24 +2114,23 @@
         <f>E13+F13</f>
         <v>118.5</v>
       </c>
+      <c r="H13">
+        <f>G13/2</f>
+        <v>59.25</v>
+      </c>
       <c r="I13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
+        <f>45-I13</f>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C14" t="s">
@@ -2020,24 +2149,23 @@
         <f>E14+F14</f>
         <v>118</v>
       </c>
+      <c r="H14">
+        <f>G14/2</f>
+        <v>59</v>
+      </c>
       <c r="I14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+        <f>45-I14</f>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C15" t="s">
@@ -2056,24 +2184,23 @@
         <f>E15+F15</f>
         <v>112.5</v>
       </c>
+      <c r="H15">
+        <f>G15/2</f>
+        <v>56.25</v>
+      </c>
       <c r="I15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+        <f>45-I15</f>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="s">
@@ -2092,24 +2219,23 @@
         <f>E16+F16</f>
         <v>106</v>
       </c>
+      <c r="H16">
+        <f>G16/2</f>
+        <v>53</v>
+      </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I16</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>11</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
@@ -2128,24 +2254,23 @@
         <f>E17+F17</f>
         <v>103</v>
       </c>
+      <c r="H17">
+        <f>G17/2</f>
+        <v>51.5</v>
+      </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I17</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>12</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
@@ -2164,24 +2289,23 @@
         <f>E18+F18</f>
         <v>101</v>
       </c>
+      <c r="H18">
+        <f>G18/2</f>
+        <v>50.5</v>
+      </c>
       <c r="I18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I18</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C19" t="s">
@@ -2200,24 +2324,23 @@
         <f>E19+F19</f>
         <v>100.5</v>
       </c>
+      <c r="H19">
+        <f>G19/2</f>
+        <v>50.25</v>
+      </c>
       <c r="I19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I19</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="s">
@@ -2236,24 +2359,26 @@
         <f>E20+F20</f>
         <v>93.5</v>
       </c>
+      <c r="H20">
+        <f>G20/2</f>
+        <v>46.75</v>
+      </c>
       <c r="I20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I20</f>
+        <v>37</v>
+      </c>
+      <c r="P20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="17" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C21" t="s">
@@ -2272,24 +2397,29 @@
         <f>E21+F21</f>
         <v>87</v>
       </c>
+      <c r="H21">
+        <f>G21/2</f>
+        <v>43.5</v>
+      </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I21</f>
+        <v>42</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="17" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>7</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
@@ -2308,24 +2438,37 @@
         <f>E22+F22</f>
         <v>79.5</v>
       </c>
+      <c r="H22">
+        <f>G22/2</f>
+        <v>39.75</v>
+      </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I22</f>
+        <v>45</v>
+      </c>
+      <c r="P22">
+        <f>P20-P21</f>
+        <v>24</v>
+      </c>
+      <c r="Q22">
+        <v>0.3</v>
+      </c>
+      <c r="R22">
+        <f>$P$22*Q22</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="17" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C23" t="s">
@@ -2344,24 +2487,33 @@
         <f>E23+F23</f>
         <v>77.5</v>
       </c>
+      <c r="H23">
+        <f>G23/2</f>
+        <v>38.75</v>
+      </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I23</f>
+        <v>45</v>
+      </c>
+      <c r="Q23">
+        <v>0.4</v>
+      </c>
+      <c r="R23">
+        <f t="shared" ref="R23:R24" si="1">$P$22*Q23</f>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="17" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C24" t="s">
@@ -2380,24 +2532,33 @@
         <f>E24+F24</f>
         <v>76</v>
       </c>
+      <c r="H24">
+        <f>G24/2</f>
+        <v>38</v>
+      </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I24</f>
+        <v>45</v>
+      </c>
+      <c r="Q24">
+        <v>0.3</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="1"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>5</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
@@ -2416,24 +2577,23 @@
         <f>E25+F25</f>
         <v>72.5</v>
       </c>
+      <c r="H25">
+        <f>G25/2</f>
+        <v>36.25</v>
+      </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I25</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>6</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C26" t="s">
@@ -2452,276 +2612,268 @@
         <f>E26+F26</f>
         <v>72</v>
       </c>
+      <c r="H26">
+        <f>G26/2</f>
+        <v>36</v>
+      </c>
       <c r="I26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27">
+        <f>45-I26</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27">
+      <c r="D27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="9">
         <v>36</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="9">
         <v>34</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="9">
         <f>E27+F27</f>
         <v>70</v>
       </c>
-      <c r="I27">
-        <v>0</v>
+      <c r="H27" s="9">
+        <f>G27/2</f>
+        <v>35</v>
+      </c>
+      <c r="I27" s="9">
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28">
+        <f>45-I27</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9">
         <v>15</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28">
+      <c r="D28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9">
         <v>28</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="9">
         <v>39</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="9">
         <f>E28+F28</f>
         <v>67</v>
       </c>
-      <c r="I28">
-        <v>0</v>
+      <c r="H28" s="9">
+        <f>G28/2</f>
+        <v>33.5</v>
+      </c>
+      <c r="I28" s="9">
+        <v>3</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I28</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F29">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G29">
         <f>E29+F29</f>
         <v>63</v>
       </c>
+      <c r="H29">
+        <f>G29/2</f>
+        <v>31.5</v>
+      </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I29</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G30">
         <f>E30+F30</f>
         <v>63</v>
       </c>
+      <c r="H30">
+        <f>G30/2</f>
+        <v>31.5</v>
+      </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31">
+        <f>45-I30</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="9">
         <v>9</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31">
+      <c r="D31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="9">
         <v>20</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="9">
         <v>42</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="9">
         <f>E31+F31</f>
         <v>62</v>
       </c>
-      <c r="I31">
+      <c r="H31" s="9">
+        <f>G31/2</f>
+        <v>31</v>
+      </c>
+      <c r="I31" s="9">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32">
+        <f>45-I31</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="9">
         <v>10</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32">
+      <c r="D32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="9">
         <v>25</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="9">
         <v>32</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="9">
         <f>E32+F32</f>
         <v>57</v>
       </c>
-      <c r="I32">
+      <c r="H32" s="9">
+        <f>G32/2</f>
+        <v>28.5</v>
+      </c>
+      <c r="I32" s="9">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33">
+        <f>45-I32</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="9">
         <v>28</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33">
+      <c r="D33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="9">
         <v>28</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="9">
         <v>28</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="9">
         <f>E33+F33</f>
         <v>56</v>
       </c>
-      <c r="I33">
+      <c r="H33" s="9">
+        <f>G33/2</f>
+        <v>28</v>
+      </c>
+      <c r="I33" s="9">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+        <f>45-I33</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>3</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="s">
@@ -2734,24 +2886,24 @@
         <f>E34+F34</f>
         <v>0</v>
       </c>
+      <c r="H34">
+        <f>G34/2</f>
+        <v>0</v>
+      </c>
       <c r="I34">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
+        <f>45-I34</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="5"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="A4:L4" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:L34">
-      <sortCondition descending="1" ref="G4"/>
+      <sortCondition descending="1" ref="H4"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
